--- a/VerveStacks_SVK_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_SVK_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SVK_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C5675F0-B22E-4102-9CE9-ECAD36F37F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2822E59-DA56-4EBA-9D24-B9B371434B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -763,16 +763,52 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_SVK_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SVK_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SVK_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SVK_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SVK_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_SVK_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_SVK_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_solelc_spv_SVK_003</t>
@@ -781,42 +817,6 @@
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_solelc_spv_SVK_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SVK_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SVK_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SVK_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SVK_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SVK_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_SVK_010</t>
   </si>
   <si>
@@ -835,30 +835,30 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w5131796-400_SVK,e_w656435549-220_SVK</t>
+  </si>
+  <si>
+    <t>e_SK6-220_SVK,e_w672771472-400_SVK,e_w639671352-220_SVK</t>
+  </si>
+  <si>
+    <t>e_SK2-400_SVK</t>
+  </si>
+  <si>
+    <t>e_w175052362-400_SVK,e_w556969469-400_SVK</t>
+  </si>
+  <si>
+    <t>e_w111687967-400_SVK,e_w203232760-400_SVK</t>
+  </si>
+  <si>
     <t>e_SK19-400_SVK,e_w666404730-400_SVK,e_r11038054-400_SVK,e_w100979306-400_SVK</t>
   </si>
   <si>
+    <t>e_w199900178-220_SVK,e_SK10-220_SVK,e_w656435549-220_SVK,e_w614130490-400_SVK</t>
+  </si>
+  <si>
     <t>e_w203232760-400_SVK,e_w666404730-400_SVK,e_w100979306-400_SVK</t>
   </si>
   <si>
-    <t>e_w5131796-400_SVK,e_w656435549-220_SVK</t>
-  </si>
-  <si>
-    <t>e_SK6-220_SVK,e_w672771472-400_SVK,e_w639671352-220_SVK</t>
-  </si>
-  <si>
-    <t>e_SK2-400_SVK</t>
-  </si>
-  <si>
-    <t>e_w199900178-220_SVK,e_SK10-220_SVK,e_w656435549-220_SVK,e_w614130490-400_SVK</t>
-  </si>
-  <si>
-    <t>e_w111687967-400_SVK,e_w203232760-400_SVK</t>
-  </si>
-  <si>
-    <t>e_w175052362-400_SVK,e_w556969469-400_SVK</t>
-  </si>
-  <si>
     <t>e_w128968280-400_SVK,e_SK24-400_SVK,e_w111687967-400_SVK</t>
   </si>
   <si>
@@ -871,48 +871,48 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_wonelc_won_SVK_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SVK_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SVK_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SVK_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SVK_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SVK_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_SVK_005</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_SVK_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SVK_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SVK_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SVK_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SVK_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SVK_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_SVK_007</t>
   </si>
   <si>
@@ -931,46 +931,46 @@
     <t>e_w666404730-400_SVK,e_w100979306-400_SVK,e_SK2-400_SVK</t>
   </si>
   <si>
+    <t>elc_won_SVK_002</t>
+  </si>
+  <si>
+    <t>e_SK19-400_SVK,e_r11038054-400_SVK,e_w175052362-400_SVK</t>
+  </si>
+  <si>
+    <t>elc_won_SVK_003</t>
+  </si>
+  <si>
+    <t>e_w128968280-400_SVK,e_SK24-400_SVK</t>
+  </si>
+  <si>
+    <t>elc_won_SVK_006</t>
+  </si>
+  <si>
+    <t>e_w229685438-400_SVK,e_SK11-220_SVK</t>
+  </si>
+  <si>
+    <t>elc_won_SVK_008</t>
+  </si>
+  <si>
+    <t>e_SK10-220_SVK,e_w614130490-400_SVK,e_SK6-220_SVK,e_w672771472-400_SVK</t>
+  </si>
+  <si>
+    <t>elc_won_SVK_001</t>
+  </si>
+  <si>
+    <t>e_w666404730-400_SVK,e_w100979306-400_SVK,e_w556969469-400_SVK</t>
+  </si>
+  <si>
+    <t>elc_won_SVK_009</t>
+  </si>
+  <si>
+    <t>e_w639671352-220_SVK,e_w203232760-400_SVK</t>
+  </si>
+  <si>
     <t>elc_won_SVK_005</t>
   </si>
   <si>
     <t>e_w111687967-400_SVK</t>
-  </si>
-  <si>
-    <t>elc_won_SVK_002</t>
-  </si>
-  <si>
-    <t>e_SK19-400_SVK,e_r11038054-400_SVK,e_w175052362-400_SVK</t>
-  </si>
-  <si>
-    <t>elc_won_SVK_009</t>
-  </si>
-  <si>
-    <t>e_w639671352-220_SVK,e_w203232760-400_SVK</t>
-  </si>
-  <si>
-    <t>elc_won_SVK_003</t>
-  </si>
-  <si>
-    <t>e_w128968280-400_SVK,e_SK24-400_SVK</t>
-  </si>
-  <si>
-    <t>elc_won_SVK_006</t>
-  </si>
-  <si>
-    <t>e_w229685438-400_SVK,e_SK11-220_SVK</t>
-  </si>
-  <si>
-    <t>elc_won_SVK_008</t>
-  </si>
-  <si>
-    <t>e_SK10-220_SVK,e_w614130490-400_SVK,e_SK6-220_SVK,e_w672771472-400_SVK</t>
-  </si>
-  <si>
-    <t>elc_won_SVK_001</t>
-  </si>
-  <si>
-    <t>e_w666404730-400_SVK,e_w100979306-400_SVK,e_w556969469-400_SVK</t>
   </si>
   <si>
     <t>elc_won_SVK_007</t>
@@ -5942,7 +5942,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1B46351-67A7-4736-AEEA-080A20524E62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03AA30E1-0BD4-4E6C-8988-7BE10CFAC55F}">
   <dimension ref="B9:AP20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6138,16 +6138,16 @@
         <v>211</v>
       </c>
       <c r="Y11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Z11" t="s">
         <v>235</v>
       </c>
       <c r="AA11">
-        <v>0.9986043298383831</v>
+        <v>0.99866504767068986</v>
       </c>
       <c r="AB11">
-        <v>25.587286296310729</v>
+        <v>24.474126037351851</v>
       </c>
       <c r="AD11" t="s">
         <v>210</v>
@@ -6248,16 +6248,16 @@
         <v>215</v>
       </c>
       <c r="Y12" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="Z12" t="s">
         <v>236</v>
       </c>
       <c r="AA12">
-        <v>0.99717955921547352</v>
+        <v>0.99840501683816196</v>
       </c>
       <c r="AB12">
-        <v>51.708081049652449</v>
+        <v>29.241357967030492</v>
       </c>
       <c r="AD12" t="s">
         <v>210</v>
@@ -6290,10 +6290,10 @@
         <v>268</v>
       </c>
       <c r="AO12">
-        <v>0.99745054218751195</v>
+        <v>0.99864406443036968</v>
       </c>
       <c r="AP12">
-        <v>46.74005989561482</v>
+        <v>24.858818776556571</v>
       </c>
     </row>
     <row r="13" spans="2:42">
@@ -6358,16 +6358,16 @@
         <v>217</v>
       </c>
       <c r="Y13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="Z13" t="s">
         <v>237</v>
       </c>
       <c r="AA13">
-        <v>0.99866504767068986</v>
+        <v>0.99741350054898348</v>
       </c>
       <c r="AB13">
-        <v>24.474126037351851</v>
+        <v>47.419156601969171</v>
       </c>
       <c r="AD13" t="s">
         <v>210</v>
@@ -6400,10 +6400,10 @@
         <v>270</v>
       </c>
       <c r="AO13">
-        <v>0.99864406443036968</v>
+        <v>0.99795936551071729</v>
       </c>
       <c r="AP13">
-        <v>24.858818776556571</v>
+        <v>37.411632303517088</v>
       </c>
     </row>
     <row r="14" spans="2:42">
@@ -6468,16 +6468,16 @@
         <v>219</v>
       </c>
       <c r="Y14" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="Z14" t="s">
         <v>238</v>
       </c>
       <c r="AA14">
-        <v>0.99840501683816196</v>
+        <v>0.99902611726101243</v>
       </c>
       <c r="AB14">
-        <v>29.241357967030492</v>
+        <v>17.854516881439864</v>
       </c>
       <c r="AD14" t="s">
         <v>210</v>
@@ -6510,10 +6510,10 @@
         <v>272</v>
       </c>
       <c r="AO14">
-        <v>0.99850369884664603</v>
+        <v>0.99861852453136835</v>
       </c>
       <c r="AP14">
-        <v>27.432187811490291</v>
+        <v>25.327050258247553</v>
       </c>
     </row>
     <row r="15" spans="2:42">
@@ -6578,16 +6578,16 @@
         <v>221</v>
       </c>
       <c r="Y15" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Z15" t="s">
         <v>239</v>
       </c>
       <c r="AA15">
-        <v>0.99741350054898348</v>
+        <v>0.99940985971006635</v>
       </c>
       <c r="AB15">
-        <v>47.419156601969171</v>
+        <v>10.819238648784395</v>
       </c>
       <c r="AD15" t="s">
         <v>210</v>
@@ -6620,10 +6620,10 @@
         <v>274</v>
       </c>
       <c r="AO15">
-        <v>0.99795936551071729</v>
+        <v>0.99828217905165062</v>
       </c>
       <c r="AP15">
-        <v>37.411632303517088</v>
+        <v>31.493384053072713</v>
       </c>
     </row>
     <row r="16" spans="2:42">
@@ -6688,16 +6688,16 @@
         <v>223</v>
       </c>
       <c r="Y16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Z16" t="s">
         <v>240</v>
       </c>
       <c r="AA16">
-        <v>0.99839465660908489</v>
+        <v>0.9986043298383831</v>
       </c>
       <c r="AB16">
-        <v>29.431295500109734</v>
+        <v>25.587286296310729</v>
       </c>
       <c r="AD16" t="s">
         <v>210</v>
@@ -6730,10 +6730,10 @@
         <v>276</v>
       </c>
       <c r="AO16">
-        <v>0.99861852453136835</v>
+        <v>0.99889812846997628</v>
       </c>
       <c r="AP16">
-        <v>25.327050258247553</v>
+        <v>20.200978050434106</v>
       </c>
     </row>
     <row r="17" spans="2:42">
@@ -6798,16 +6798,16 @@
         <v>225</v>
       </c>
       <c r="Y17" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Z17" t="s">
         <v>241</v>
       </c>
       <c r="AA17">
-        <v>0.99940985971006635</v>
+        <v>0.99839465660908489</v>
       </c>
       <c r="AB17">
-        <v>10.819238648784395</v>
+        <v>29.431295500109734</v>
       </c>
       <c r="AD17" t="s">
         <v>210</v>
@@ -6840,10 +6840,10 @@
         <v>278</v>
       </c>
       <c r="AO17">
-        <v>0.99828217905165062</v>
+        <v>0.99850369884664603</v>
       </c>
       <c r="AP17">
-        <v>31.493384053072713</v>
+        <v>27.432187811490291</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -6908,16 +6908,16 @@
         <v>227</v>
       </c>
       <c r="Y18" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Z18" t="s">
         <v>242</v>
       </c>
       <c r="AA18">
-        <v>0.99902611726101243</v>
+        <v>0.99717955921547352</v>
       </c>
       <c r="AB18">
-        <v>17.854516881439864</v>
+        <v>51.708081049652449</v>
       </c>
       <c r="AD18" t="s">
         <v>210</v>
@@ -6950,10 +6950,10 @@
         <v>280</v>
       </c>
       <c r="AO18">
-        <v>0.99889812846997628</v>
+        <v>0.99745054218751195</v>
       </c>
       <c r="AP18">
-        <v>20.200978050434106</v>
+        <v>46.74005989561482</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7182,7 +7182,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E01799C-E065-4F32-AE09-4EC3CFA591DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEDE11F-254F-453A-BC7F-EAB88367BE14}">
   <dimension ref="B9:M20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7255,7 +7255,7 @@
         <v>285</v>
       </c>
       <c r="K11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L11">
         <v>16.456003352043751</v>
@@ -7290,7 +7290,7 @@
         <v>287</v>
       </c>
       <c r="K12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L12">
         <v>10.728122120068091</v>
@@ -7325,7 +7325,7 @@
         <v>289</v>
       </c>
       <c r="K13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L13">
         <v>9.074958724763615</v>
@@ -7395,7 +7395,7 @@
         <v>293</v>
       </c>
       <c r="K15" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L15">
         <v>3.2217559948664833</v>
@@ -7430,7 +7430,7 @@
         <v>295</v>
       </c>
       <c r="K16" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="L16">
         <v>12.065476972844859</v>
@@ -7500,7 +7500,7 @@
         <v>299</v>
       </c>
       <c r="K18" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L18">
         <v>26.069534128786131</v>
@@ -7535,7 +7535,7 @@
         <v>301</v>
       </c>
       <c r="K19" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="L19">
         <v>11.484700191337225</v>
@@ -7585,7 +7585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49710138-E0DF-4DB7-B9EF-CB4CDB743A09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56F693A-FB6C-4D4E-901B-343D6014A75A}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9402,7 +9402,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BADB83A-E423-4B06-9598-C45FFEED4D7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005940BA-E9F3-4E9A-B92E-25F9EABB513A}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
